--- a/data/shsh_js/wind.xlsx
+++ b/data/shsh_js/wind.xlsx
@@ -439,277 +439,277 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45973.58333333334</v>
+        <v>46068.66666666666</v>
       </c>
       <c r="B2" t="n">
-        <v>49.00000000000001</v>
+        <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45973.625</v>
+        <v>46068.70833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>50.99999999999999</v>
+        <v>90</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45973.66666666666</v>
+        <v>46068.75</v>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45973.70833333334</v>
+        <v>46068.79166666666</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45973.75</v>
+        <v>46068.83333333334</v>
       </c>
       <c r="B6" t="n">
-        <v>37.99999999999999</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45973.79166666666</v>
+        <v>46068.875</v>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>58.99999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45973.83333333334</v>
+        <v>46068.91666666666</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>50.99999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45973.875</v>
+        <v>46068.95833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45973.91666666666</v>
+        <v>46069</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45973.95833333334</v>
+        <v>46069.04166666666</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>40.99999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45974</v>
+        <v>46069.08333333334</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45974.04166666666</v>
+        <v>46069.125</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45974.08333333334</v>
+        <v>46069.16666666666</v>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45974.125</v>
+        <v>46069.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45974.16666666666</v>
+        <v>46069.25</v>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45974.20833333334</v>
+        <v>46069.29166666666</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45974.25</v>
+        <v>46069.33333333334</v>
       </c>
       <c r="B18" t="n">
-        <v>346</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45974.29166666666</v>
+        <v>46069.375</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45974.33333333334</v>
+        <v>46069.41666666666</v>
       </c>
       <c r="B20" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45974.375</v>
+        <v>46069.45833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>40.99999999999999</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45974.41666666666</v>
+        <v>46069.5</v>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45974.45833333334</v>
+        <v>46069.54166666666</v>
       </c>
       <c r="B23" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45974.5</v>
+        <v>46069.58333333334</v>
       </c>
       <c r="B24" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45974.54166666666</v>
+        <v>46069.625</v>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>340</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45974.58333333334</v>
+        <v>46069.66666666666</v>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>345</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/shsh_js/wind.xlsx
+++ b/data/shsh_js/wind.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,277 +439,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46068.66666666666</v>
+        <v>46126.33333333334</v>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>309</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46068.70833333334</v>
+        <v>46126.375</v>
       </c>
       <c r="B3" t="n">
-        <v>90</v>
+        <v>292</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46068.75</v>
+        <v>46126.41666666666</v>
       </c>
       <c r="B4" t="n">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46068.79166666666</v>
+        <v>46126.45833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="C5" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46068.83333333334</v>
+        <v>46126.5</v>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46068.875</v>
+        <v>46126.54166666666</v>
       </c>
       <c r="B7" t="n">
-        <v>58.99999999999999</v>
+        <v>298.9999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46068.91666666666</v>
+        <v>46126.58333333334</v>
       </c>
       <c r="B8" t="n">
-        <v>50.99999999999999</v>
+        <v>312.9999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46068.95833333334</v>
+        <v>46126.625</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="C9" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46069</v>
+        <v>46126.66666666666</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="C10" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46069.04166666666</v>
+        <v>46126.70833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>40.99999999999999</v>
+        <v>297</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46069.08333333334</v>
+        <v>46126.75</v>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>289</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46069.125</v>
+        <v>46126.79166666666</v>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c r="C13" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46069.16666666666</v>
+        <v>46126.83333333334</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>279</v>
       </c>
       <c r="C14" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46069.20833333334</v>
-      </c>
-      <c r="B15" t="n">
-        <v>27</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46069.25</v>
-      </c>
-      <c r="B16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46069.29166666666</v>
-      </c>
-      <c r="B17" t="n">
-        <v>25</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46069.33333333334</v>
-      </c>
-      <c r="B18" t="n">
-        <v>25</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46069.375</v>
-      </c>
-      <c r="B19" t="n">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46069.41666666666</v>
-      </c>
-      <c r="B20" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46069.45833333334</v>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
         <v>2.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46069.5</v>
-      </c>
-      <c r="B22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46069.54166666666</v>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46069.58333333334</v>
-      </c>
-      <c r="B24" t="n">
-        <v>7</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46069.625</v>
-      </c>
-      <c r="B25" t="n">
-        <v>340</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46069.66666666666</v>
-      </c>
-      <c r="B26" t="n">
-        <v>345</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/shsh_js/wind.xlsx
+++ b/data/shsh_js/wind.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,145 +439,376 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46126.33333333334</v>
+        <v>46045.41666666666</v>
       </c>
       <c r="B2" t="n">
-        <v>309</v>
+        <v>215</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46126.375</v>
+        <v>46045.45833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46126.41666666666</v>
+        <v>46045.5</v>
       </c>
       <c r="B4" t="n">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46126.45833333334</v>
+        <v>46045.54166666666</v>
       </c>
       <c r="B5" t="n">
-        <v>294</v>
+        <v>197</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46126.5</v>
+        <v>46045.58333333334</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46126.54166666666</v>
+        <v>46045.625</v>
       </c>
       <c r="B7" t="n">
-        <v>298.9999999999999</v>
+        <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46126.58333333334</v>
+        <v>46045.66666666666</v>
       </c>
       <c r="B8" t="n">
-        <v>312.9999999999999</v>
+        <v>239</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46126.625</v>
+        <v>46045.70833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>309</v>
+        <v>239.9999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46126.66666666666</v>
+        <v>46045.75</v>
       </c>
       <c r="B10" t="n">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="C10" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46126.70833333334</v>
+        <v>46045.79166666666</v>
       </c>
       <c r="B11" t="n">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="C11" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46126.75</v>
+        <v>46045.83333333334</v>
       </c>
       <c r="B12" t="n">
-        <v>289</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46126.79166666666</v>
+        <v>46045.875</v>
       </c>
       <c r="B13" t="n">
-        <v>277</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46126.83333333334</v>
+        <v>46045.91666666666</v>
       </c>
       <c r="B14" t="n">
-        <v>279</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46045.95833333334</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46046</v>
+      </c>
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46046.04166666666</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46046.08333333334</v>
+      </c>
+      <c r="B18" t="n">
+        <v>34</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46046.125</v>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46046.16666666666</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46046.20833333334</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46046.25</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46046.29166666666</v>
+      </c>
+      <c r="B23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46046.33333333334</v>
+      </c>
+      <c r="B24" t="n">
+        <v>36</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46046.375</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58.99999999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46046.41666666666</v>
+      </c>
+      <c r="B26" t="n">
+        <v>81.99999999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46046.45833333334</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46046.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46046.54166666666</v>
+      </c>
+      <c r="B29" t="n">
+        <v>104</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46046.58333333334</v>
+      </c>
+      <c r="B30" t="n">
+        <v>122</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46046.625</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46046.66666666666</v>
+      </c>
+      <c r="B32" t="n">
+        <v>105</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46046.70833333334</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46046.75</v>
+      </c>
+      <c r="B34" t="n">
+        <v>102</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46046.79166666666</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/shsh_js/wind.xlsx
+++ b/data/shsh_js/wind.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,376 +439,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46045.41666666666</v>
+        <v>46121.29166666666</v>
       </c>
       <c r="B2" t="n">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46045.45833333334</v>
+        <v>46121.33333333334</v>
       </c>
       <c r="B3" t="n">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46045.5</v>
+        <v>46121.375</v>
       </c>
       <c r="B4" t="n">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46045.54166666666</v>
+        <v>46121.41666666666</v>
       </c>
       <c r="B5" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46045.58333333334</v>
+        <v>46121.45833333334</v>
       </c>
       <c r="B6" t="n">
-        <v>194</v>
+        <v>247</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46045.625</v>
+        <v>46121.5</v>
       </c>
       <c r="B7" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46045.66666666666</v>
+        <v>46121.54166666666</v>
       </c>
       <c r="B8" t="n">
-        <v>239</v>
+        <v>243.9999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46045.70833333334</v>
+        <v>46121.58333333334</v>
       </c>
       <c r="B9" t="n">
-        <v>239.9999999999999</v>
+        <v>238</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46045.75</v>
+        <v>46121.625</v>
       </c>
       <c r="B10" t="n">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46045.79166666666</v>
+        <v>46121.66666666666</v>
       </c>
       <c r="B11" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C11" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46045.83333333334</v>
+        <v>46121.70833333334</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>234</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46045.875</v>
+        <v>46121.75</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46045.91666666666</v>
+        <v>46121.79166666666</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>284</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46045.95833333334</v>
-      </c>
-      <c r="B15" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46046</v>
-      </c>
-      <c r="B16" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46046.04166666666</v>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46046.08333333334</v>
-      </c>
-      <c r="B18" t="n">
-        <v>34</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46046.125</v>
-      </c>
-      <c r="B19" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46046.16666666666</v>
-      </c>
-      <c r="B20" t="n">
-        <v>9</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46046.20833333334</v>
-      </c>
-      <c r="B21" t="n">
-        <v>9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46046.25</v>
-      </c>
-      <c r="B22" t="n">
-        <v>9</v>
-      </c>
-      <c r="C22" t="n">
         <v>1.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46046.29166666666</v>
-      </c>
-      <c r="B23" t="n">
-        <v>13</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46046.33333333334</v>
-      </c>
-      <c r="B24" t="n">
-        <v>36</v>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46046.375</v>
-      </c>
-      <c r="B25" t="n">
-        <v>58.99999999999999</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46046.41666666666</v>
-      </c>
-      <c r="B26" t="n">
-        <v>81.99999999999999</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46046.45833333334</v>
-      </c>
-      <c r="B27" t="n">
-        <v>106</v>
-      </c>
-      <c r="C27" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46046.5</v>
-      </c>
-      <c r="B28" t="n">
-        <v>106</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46046.54166666666</v>
-      </c>
-      <c r="B29" t="n">
-        <v>104</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46046.58333333334</v>
-      </c>
-      <c r="B30" t="n">
-        <v>122</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46046.625</v>
-      </c>
-      <c r="B31" t="n">
-        <v>104</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46046.66666666666</v>
-      </c>
-      <c r="B32" t="n">
-        <v>105</v>
-      </c>
-      <c r="C32" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46046.70833333334</v>
-      </c>
-      <c r="B33" t="n">
-        <v>107</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46046.75</v>
-      </c>
-      <c r="B34" t="n">
-        <v>102</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46046.79166666666</v>
-      </c>
-      <c r="B35" t="n">
-        <v>96</v>
-      </c>
-      <c r="C35" t="n">
-        <v>4.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/shsh_js/wind.xlsx
+++ b/data/shsh_js/wind.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,145 +439,156 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46121.29166666666</v>
+        <v>46186</v>
       </c>
       <c r="B2" t="n">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46121.33333333334</v>
+        <v>46186.04166666666</v>
       </c>
       <c r="B3" t="n">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46121.375</v>
+        <v>46186.08333333334</v>
       </c>
       <c r="B4" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46121.41666666666</v>
+        <v>46186.125</v>
       </c>
       <c r="B5" t="n">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46121.45833333334</v>
+        <v>46186.16666666666</v>
       </c>
       <c r="B6" t="n">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46121.5</v>
+        <v>46186.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46121.54166666666</v>
+        <v>46186.25</v>
       </c>
       <c r="B8" t="n">
-        <v>243.9999999999999</v>
+        <v>206</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46121.58333333334</v>
+        <v>46186.29166666666</v>
       </c>
       <c r="B9" t="n">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46121.625</v>
+        <v>46186.33333333334</v>
       </c>
       <c r="B10" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C10" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46121.66666666666</v>
+        <v>46186.375</v>
       </c>
       <c r="B11" t="n">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="C11" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46121.70833333334</v>
+        <v>46186.41666666666</v>
       </c>
       <c r="B12" t="n">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="C12" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46121.75</v>
+        <v>46186.45833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>257</v>
+        <v>187</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46121.79166666666</v>
+        <v>46186.5</v>
       </c>
       <c r="B14" t="n">
-        <v>284</v>
+        <v>183</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46186.54166666666</v>
+      </c>
+      <c r="B15" t="n">
+        <v>201</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/shsh_js/wind.xlsx
+++ b/data/shsh_js/wind.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,156 +439,145 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46186</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B2" t="n">
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46186.04166666666</v>
+        <v>46212.125</v>
       </c>
       <c r="B3" t="n">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46186.08333333334</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B4" t="n">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46186.125</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46186.16666666666</v>
+        <v>46212.25</v>
       </c>
       <c r="B6" t="n">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46186.20833333334</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B7" t="n">
-        <v>212</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46186.25</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46186.29166666666</v>
+        <v>46212.375</v>
       </c>
       <c r="B9" t="n">
-        <v>211</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46186.33333333334</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46186.375</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>194</v>
+        <v>64</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46186.41666666666</v>
+        <v>46212.5</v>
       </c>
       <c r="B12" t="n">
-        <v>186</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46186.45833333334</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B13" t="n">
-        <v>187</v>
+        <v>85</v>
       </c>
       <c r="C13" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46186.5</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B14" t="n">
-        <v>183</v>
+        <v>99.00000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46186.54166666666</v>
-      </c>
-      <c r="B15" t="n">
-        <v>201</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
